--- a/Intro materials/Tentative Schedule (Spring 2026).xlsx
+++ b/Intro materials/Tentative Schedule (Spring 2026).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Library/CloudStorage/Dropbox/Clemson/Econometrics Course/Specific to Semesters/Spring 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/Intro materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB96DAA5-D165-0146-98ED-E1E55F06DBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65F02BA-34D4-0745-A1E4-201D941EA74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
@@ -76,12 +76,6 @@
     <t>Spring Break (No Class)</t>
   </si>
   <si>
-    <t>Coding Midterm (No Class)</t>
-  </si>
-  <si>
-    <t>In Class Theory Midterm</t>
-  </si>
-  <si>
     <t>1-page final project proposal due (No Class)</t>
   </si>
   <si>
@@ -101,6 +95,12 @@
   </si>
   <si>
     <t>Meet 1-1 to discuss final projects (office hours)</t>
+  </si>
+  <si>
+    <t>Coding Midterm</t>
+  </si>
+  <si>
+    <t>Theory Midterm</t>
   </si>
 </sst>
 </file>
@@ -575,7 +575,7 @@
         <v>46056</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -584,7 +584,7 @@
         <v>46058</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -593,7 +593,7 @@
         <v>46063</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -602,7 +602,7 @@
         <v>46065</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -638,7 +638,7 @@
         <v>46079</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -701,7 +701,7 @@
         <v>46105</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -710,7 +710,7 @@
         <v>46107</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -719,7 +719,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -728,7 +728,7 @@
         <v>46114</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -773,7 +773,7 @@
         <v>46133</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">

--- a/Intro materials/Tentative Schedule (Spring 2026).xlsx
+++ b/Intro materials/Tentative Schedule (Spring 2026).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/Intro materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65F02BA-34D4-0745-A1E4-201D941EA74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8556A933-774B-ED41-9C1B-E329119E11C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
@@ -714,21 +714,21 @@
       </c>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
+      <c r="A25" s="7">
         <f t="shared" si="0"/>
         <v>46112</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6">
+        <f t="shared" si="0"/>
+        <v>46114</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7">
-        <f t="shared" si="0"/>
-        <v>46114</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">

--- a/Intro materials/Tentative Schedule (Spring 2026).xlsx
+++ b/Intro materials/Tentative Schedule (Spring 2026).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/Intro materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Library/CloudStorage/Dropbox/Clemson/Econometrics Course/Specific to Semesters/Spring 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8556A933-774B-ED41-9C1B-E329119E11C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966D7789-5A87-114B-9CB8-CE7E26C80611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{72D0DB20-A265-EC45-9D54-DA8133B16545}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Introduction</t>
   </si>
@@ -79,9 +79,6 @@
     <t>1-page final project proposal due (No Class)</t>
   </si>
   <si>
-    <t>Midterm Review</t>
-  </si>
-  <si>
     <t>Sampling/ Confidence Intervals and Hypothesis Testing</t>
   </si>
   <si>
@@ -101,6 +98,12 @@
   </si>
   <si>
     <t>Theory Midterm</t>
+  </si>
+  <si>
+    <t>No Class</t>
+  </si>
+  <si>
+    <t>Panel Data/ Difference-in-Differences</t>
   </si>
 </sst>
 </file>
@@ -575,7 +578,7 @@
         <v>46056</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -593,7 +596,7 @@
         <v>46063</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -602,7 +605,7 @@
         <v>46065</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -638,7 +641,7 @@
         <v>46079</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -655,8 +658,8 @@
         <f t="shared" si="0"/>
         <v>46086</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>7</v>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -674,7 +677,7 @@
         <v>46093</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -701,7 +704,7 @@
         <v>46105</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -710,7 +713,7 @@
         <v>46107</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -719,7 +722,7 @@
         <v>46112</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -728,7 +731,7 @@
         <v>46114</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -773,7 +776,7 @@
         <v>46133</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
